--- a/hourly datasets/cap_gen_year5final.xlsx
+++ b/hourly datasets/cap_gen_year5final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09280751105506574</v>
+        <v>0.08961079781231389</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.103151799219635</v>
+        <v>0.102187391294374</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1959593102747007</v>
+        <v>0.1917981891066879</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09048863435816971</v>
+        <v>0.0911785807184974</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1832961454132355</v>
+        <v>0.1807893785308113</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06387097079667473</v>
+        <v>0.05942320655244451</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006256020468073837</v>
+        <v>0.005489396421033406</v>
       </c>
       <c r="D5" t="n">
-        <v>10.61619576591366</v>
+        <v>10.73330774234397</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06818126676673325</v>
+        <v>0.05851398938374813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05158639374718649</v>
+        <v>0.04864367860117936</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07615554784616198</v>
+        <v>0.07020273450370976</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1566784818517405</v>
+        <v>0.1490340043647584</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04005464743891991</v>
+        <v>0.0343635389249352</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004456084037186648</v>
+        <v>0.003181221899653866</v>
       </c>
       <c r="D6" t="n">
-        <v>4.713788261422956</v>
+        <v>4.460494355660367</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03321303009358303</v>
+        <v>0.02138636623543799</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03131215345572928</v>
+        <v>0.02812494509917765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04879714142210963</v>
+        <v>0.04060213275069292</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1328621584939856</v>
+        <v>0.1239743367372491</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03111834027607828</v>
+        <v>0.02465090103142364</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -595,7 +595,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.123925851331144</v>
+        <v>0.1142616988437375</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02732859978610495</v>
+        <v>0.02017326483354753</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002703184104130505</v>
+        <v>0.001576226088762638</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616546450868733</v>
+        <v>2.007801522401209</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01354470906404969</v>
+        <v>0.003899533528308185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02202435973850002</v>
+        <v>0.01708223337631831</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0326328398337099</v>
+        <v>0.0232642962907764</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1201361108411707</v>
+        <v>0.1097840626458614</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02521493548482489</v>
+        <v>0.01592878410071346</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002887811832640039</v>
+        <v>0.001673668430101849</v>
       </c>
       <c r="D9" t="n">
-        <v>2.13909171682071</v>
+        <v>1.372109018574412</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01819187325317444</v>
+        <v>0.008028586103258005</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01954940697130819</v>
+        <v>0.01264729131336691</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0308804639983412</v>
+        <v>0.01921027688805965</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1180224465398906</v>
+        <v>0.1055395819130274</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02450256121722537</v>
+        <v>0.01511295985522425</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002623639709169693</v>
+        <v>0.001469179513232224</v>
       </c>
       <c r="D10" t="n">
-        <v>1.884502709513444</v>
+        <v>1.085733055629885</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01780690246746566</v>
+        <v>0.007809468542595592</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01935504060988099</v>
+        <v>0.0122321277212997</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02965008182456945</v>
+        <v>0.01799379198914854</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1173100722722911</v>
+        <v>0.1047237576675381</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03298186556308941</v>
+        <v>0.03269485392689534</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1257893766181551</v>
+        <v>0.1223056517392092</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0491487951751833</v>
+        <v>0.04749578263345115</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.141956306230249</v>
+        <v>0.137106580445765</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06100490878150903</v>
+        <v>0.05677025876185512</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1538124198365748</v>
+        <v>0.146381056574169</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06606352031034302</v>
+        <v>0.06290300431534653</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1588710313654088</v>
+        <v>0.1525138021276604</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07210076590075497</v>
+        <v>0.06940626267693976</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1649082769558207</v>
+        <v>0.1590170604892537</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07739935413739364</v>
+        <v>0.07447146247262838</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1702068651924594</v>
+        <v>0.1640822602849423</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07893862506383548</v>
+        <v>0.07648937960615788</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1717461361189012</v>
+        <v>0.1661001774184718</v>
       </c>
     </row>
     <row r="18">
@@ -815,22 +815,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09280751105506574</v>
+        <v>-0.08961079781231389</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01092901732207689</v>
+        <v>0.01039487674969329</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.51209139823487</v>
+        <v>-16.29795343171423</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04191690866172165</v>
+        <v>0.04114443696813389</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1142767561183235</v>
+        <v>-0.1100276833602711</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07133826599180827</v>
+        <v>-0.06919391226435724</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07884046889105732</v>
+        <v>0.07711162053665392</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +851,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1716479799461231</v>
+        <v>0.1667224183489678</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08467423743518479</v>
+        <v>0.08132782565751584</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +869,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1774817484902505</v>
+        <v>0.1709386234698297</v>
       </c>
     </row>
     <row r="21">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08772785525910158</v>
+        <v>0.0843076592594128</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -887,7 +887,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1805353663141673</v>
+        <v>0.1739184570717267</v>
       </c>
     </row>
     <row r="22">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09058560586556964</v>
+        <v>0.08770542672845089</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -905,7 +905,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1833931169206354</v>
+        <v>0.1773162245407648</v>
       </c>
     </row>
     <row r="23">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09369842156729383</v>
+        <v>0.09130425904155923</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -923,7 +923,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1865059326223596</v>
+        <v>0.1809150568538731</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +933,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09608927244233402</v>
+        <v>0.0951648638369256</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008627719292247897</v>
+        <v>0.008453290841330143</v>
       </c>
       <c r="D24" t="n">
-        <v>223035066761.7094</v>
+        <v>216873629143.5695</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05386315405091487</v>
+        <v>0.05772512218814899</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07913560427109874</v>
+        <v>0.07855490507906901</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1130429406135694</v>
+        <v>0.1117748225947824</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1888967834973997</v>
+        <v>0.1847756616492395</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.09713797541985594</v>
+        <v>0.09574141241814849</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008427197005246143</v>
+        <v>0.008256150330222513</v>
       </c>
       <c r="D25" t="n">
-        <v>465908856722.3784</v>
+        <v>452428369003.1914</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05166444712238601</v>
+        <v>0.05178788874349751</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08057705399739304</v>
+        <v>0.07951844455004649</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1136988968423189</v>
+        <v>0.1119643802862504</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1899454864749217</v>
+        <v>0.1853522102304624</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +989,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.100270206048319</v>
+        <v>0.09853943959518154</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008697650599882477</v>
+        <v>0.008429553965470805</v>
       </c>
       <c r="D26" t="n">
-        <v>590819431733.5083</v>
+        <v>574507023078.752</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05710141576481517</v>
+        <v>0.05586531010476686</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08318171286105486</v>
+        <v>0.08197734926830516</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1173586992355835</v>
+        <v>0.1151015299220585</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1930777171033847</v>
+        <v>0.1881502374074954</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1017,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1053440025506479</v>
+        <v>0.105568895907551</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008939364405148918</v>
+        <v>0.00872724286219447</v>
       </c>
       <c r="D27" t="n">
-        <v>587199074062.0693</v>
+        <v>570122646597.2515</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04922793667344875</v>
+        <v>0.04693782370144924</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08777675243249138</v>
+        <v>0.08842022055437058</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1229112526688048</v>
+        <v>0.1227175712607322</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1981515136057136</v>
+        <v>0.1951796937198649</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1045,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1017496236079487</v>
+        <v>0.1014717908688602</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008846132272907111</v>
+        <v>0.00882421222759101</v>
       </c>
       <c r="D28" t="n">
-        <v>16.87761100610693</v>
+        <v>17.01526792696817</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07632351879072788</v>
+        <v>0.07212339582238551</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08437087950573437</v>
+        <v>0.08413528654143407</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1191283677101631</v>
+        <v>0.1188082951962861</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1945571346630145</v>
+        <v>0.1910825886811741</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1073,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0304729534264252</v>
+        <v>0.01835625624348671</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003074019037222985</v>
+        <v>0.002092851429716713</v>
       </c>
       <c r="D29" t="n">
-        <v>3.384110462072563</v>
+        <v>2.141587797409675</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01694674548598612</v>
+        <v>0.0107968691788313</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02443253681086965</v>
+        <v>0.01424344797115806</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03651337004198098</v>
+        <v>0.02246906451581529</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1232804644814909</v>
+        <v>0.1079670540558006</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year5final.xlsx
+++ b/hourly datasets/cap_gen_year5final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2203111313342093</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.08961079781231389</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.08843180984268301</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.102187391294374</v>
+        <v>0.3556381988236283</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1917981891066879</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2237588773321021</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0911785807184974</v>
+        <v>0.356586665414232</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1807893785308113</v>
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2247073439227057</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05942320655244451</v>
+        <v>0.3630280746530455</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005489396421033406</v>
+        <v>0.006647705203509964</v>
       </c>
       <c r="D5" t="n">
-        <v>10.73330774234397</v>
+        <v>12.27346155500954</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05851398938374813</v>
+        <v>0.06270673049065963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04864367860117936</v>
+        <v>0.05207976756389006</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07020273450370976</v>
+        <v>0.07818752853417175</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1490340043647584</v>
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2311487531615193</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0343635389249352</v>
+        <v>0.3387935195558395</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003181221899653866</v>
+        <v>0.00551311770833428</v>
       </c>
       <c r="D6" t="n">
-        <v>4.460494355660367</v>
+        <v>7.179102493145085</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02138636623543799</v>
+        <v>0.07301707607380453</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02812494509917765</v>
+        <v>0.03626394836355301</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04060213275069292</v>
+        <v>0.05788685245136362</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1239743367372491</v>
+        <v>40</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2069141980643132</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +607,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02465090103142364</v>
+        <v>0.3336375815062624</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -595,7 +615,10 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1142616988437375</v>
+        <v>40</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2017582600147362</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02017326483354753</v>
+        <v>0.3281690335863391</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001576226088762638</v>
+        <v>0.0039962724575776</v>
       </c>
       <c r="D8" t="n">
-        <v>2.007801522401209</v>
+        <v>5.698663993339193</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003899533528308185</v>
+        <v>0.004318401692143605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01708223337631831</v>
+        <v>0.02542157680149979</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0232642962907764</v>
+        <v>0.04109504729763108</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1097840626458614</v>
+        <v>40</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1962897120948128</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01592878410071346</v>
+        <v>0.3277998528281674</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001673668430101849</v>
+        <v>0.004209174430214758</v>
       </c>
       <c r="D9" t="n">
-        <v>1.372109018574412</v>
+        <v>5.412530237471556</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008028586103258005</v>
+        <v>0.008921946918547002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01264729131336691</v>
+        <v>0.02128799588773031</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01921027688805965</v>
+        <v>0.03779502849945459</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1055395819130274</v>
+        <v>40</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1959205313366411</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01511295985522425</v>
+        <v>0.3262678175524385</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001469179513232224</v>
+        <v>0.003922871764442828</v>
       </c>
       <c r="D10" t="n">
-        <v>1.085733055629885</v>
+        <v>5.872074525259775</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007809468542595592</v>
+        <v>0.008867132122516027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0122321277212997</v>
+        <v>0.02249665395540024</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01799379198914854</v>
+        <v>0.03788159419505761</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1047237576675381</v>
+        <v>40</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1943884960609122</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03269485392689534</v>
+        <v>0.2610335576262277</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1223056517392092</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1291542361347015</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04749578263345115</v>
+        <v>0.2826941756101889</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.137106580445765</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1508148541186627</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05677025876185512</v>
+        <v>0.2959632617784921</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.146381056574169</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1640839402869658</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06290300431534653</v>
+        <v>0.3049138266396539</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1525138021276604</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1730345051481277</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06940626267693976</v>
+        <v>0.3131885903885608</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1590170604892537</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1813092688970346</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07447146247262838</v>
+        <v>0.3197935187604098</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1640822602849423</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1879141972688836</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07648937960615788</v>
+        <v>0.3252991382881987</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1661001774184718</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1934198167966725</v>
       </c>
     </row>
     <row r="18">
@@ -815,24 +868,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.08961079781231389</v>
+        <v>0.1318793214915263</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01039487674969329</v>
+        <v>0.01004193251745106</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.29795343171423</v>
+        <v>-16.184369472293</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04114443696813389</v>
+        <v>0.03994817569212149</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1100276833602711</v>
+        <v>-0.1080430735596433</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.06919391226435724</v>
+        <v>-0.06859481497569402</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,7 +899,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07711162053665392</v>
+        <v>0.3269885195599885</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +907,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1667224183489678</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1951091980684623</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +920,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08132782565751584</v>
+        <v>0.3293200091632382</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +928,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1709386234698297</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.197440687671712</v>
       </c>
     </row>
     <row r="21">
@@ -879,7 +941,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0843076592594128</v>
+        <v>0.3337230184961968</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -887,7 +949,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1739184570717267</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2018436970046705</v>
       </c>
     </row>
     <row r="22">
@@ -897,7 +962,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08770542672845089</v>
+        <v>0.3369209276146958</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -905,7 +970,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1773162245407648</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2050416061231695</v>
       </c>
     </row>
     <row r="23">
@@ -915,7 +983,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09130425904155923</v>
+        <v>0.3432776228784897</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -923,7 +991,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1809150568538731</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2113983013869634</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +1004,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0951648638369256</v>
+        <v>0.3485338032844686</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008453290841330143</v>
+        <v>0.008421806066166068</v>
       </c>
       <c r="D24" t="n">
-        <v>216873629143.5695</v>
+        <v>216862862756.5623</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05772512218814899</v>
+        <v>0.05763883219023262</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07855490507906901</v>
+        <v>0.07820718643927396</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1117748225947824</v>
+        <v>0.1113034123798111</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1847756616492395</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2166544817929424</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +1035,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.09574141241814849</v>
+        <v>0.3541488933818344</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008256150330222513</v>
+        <v>0.008235224483556566</v>
       </c>
       <c r="D25" t="n">
-        <v>452428369003.1914</v>
+        <v>452399533069.7952</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05178788874349751</v>
+        <v>0.05169796929921434</v>
       </c>
       <c r="F25" t="n">
-        <v>0.07951844455004649</v>
+        <v>0.07927638598510373</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1119643802862504</v>
+        <v>0.1116400909096035</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1853522102304624</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2222695718903081</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +1066,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09853943959518154</v>
+        <v>0.3591563605712302</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008429553965470805</v>
+        <v>0.008405217358243119</v>
       </c>
       <c r="D26" t="n">
-        <v>574507023078.752</v>
+        <v>574462021277.9414</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05586531010476686</v>
+        <v>0.05567069240844064</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08197734926830516</v>
+        <v>0.08171839824652638</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1151015299220585</v>
+        <v>0.1147468886579256</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1881502374074954</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.227277039079704</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1097,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.105568895907551</v>
+        <v>0.3652033753109317</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00872724286219447</v>
+        <v>0.008641249948947244</v>
       </c>
       <c r="D27" t="n">
-        <v>570122646597.2515</v>
+        <v>570067008951.9451</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04693782370144924</v>
+        <v>0.04682086476733387</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08842022055437058</v>
+        <v>0.08748155442156567</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1227175712607322</v>
+        <v>0.1214411806770844</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1951796937198649</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2333240538194055</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1128,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1014717908688602</v>
+        <v>0.3612594554216761</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00882421222759101</v>
+        <v>0.008680157768430981</v>
       </c>
       <c r="D28" t="n">
-        <v>17.01526792696817</v>
+        <v>16.84166399417041</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07212339582238551</v>
+        <v>0.07163406787148345</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08413528654143407</v>
+        <v>0.08278900948565797</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1188082951962861</v>
+        <v>0.1168961407402962</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1910825886811741</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2293801339301499</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1159,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01835625624348671</v>
+        <v>0.3307595471003605</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002092851429716713</v>
+        <v>0.004647928413803498</v>
       </c>
       <c r="D29" t="n">
-        <v>2.141587797409675</v>
+        <v>7.639535178524219</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0107968691788313</v>
+        <v>0.01214499074784282</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01424344797115806</v>
+        <v>0.02603653636127477</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02246906451581529</v>
+        <v>0.04429226320419685</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1079670540558006</v>
+        <v>40</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1988802256088342</v>
       </c>
     </row>
   </sheetData>
